--- a/backend/truck_tyre_specialists_additional.xlsx
+++ b/backend/truck_tyre_specialists_additional.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,12 +491,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>UK's leading commercial vehicle tyre management group. 300+ technicians, 42 depots nationwide. Michelin-owned. ~£103.5M turnover.</t>
+          <t>National truck tyre management specialist for trucks, trailers, buses, coaches. Part of Euromaster/Michelin Group. ~£103.5M turnover, 546 employees. 24/7/365 emergency roadside response.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>tructyre.co.uk</t>
+          <t>www.tructyre.co.uk</t>
         </is>
       </c>
     </row>
@@ -533,12 +533,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Michelin subsidiary. Was UK's largest tyre distributor with 260+ centres. Currently winding down UK operations. Major truck/commercial tyre service.</t>
+          <t>UK's largest tyre service provider (Michelin subsidiary). ~340 centres, 820+ service vans, 2,600 employees. Major commercial/truck tyre operations with 24/7 breakdown response (96,000+ call-outs/year).</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>atseuromaster.co.uk</t>
+          <t>www.atseuromaster.co.uk</t>
         </is>
       </c>
     </row>
@@ -575,14 +575,10 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>UK's leading truck tyre wholesale distributor. Est. 1990. Supplies ~1 in 10 replacement truck tyres fitted in UK. 50,000+ truck tyres in stock.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>internationaltyres.com</t>
-        </is>
-      </c>
+          <t>UK's leading truck tyre wholesaler. Major supplier of commercial vehicle tyres to the UK trade.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -617,12 +613,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>UK's largest independent OTR (Off-The-Road) tyre dealer. Services quarries, waste contractors, ports. Canadian parent. In UK since 1977.</t>
+          <t>World's largest independent tyre dealer. UK operations focused on OTR (off-the-road) and mining tyre specialist services for heavy equipment and commercial vehicles.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>kaltiremining.com</t>
+          <t>www.kaltire.com</t>
         </is>
       </c>
     </row>
@@ -659,12 +655,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Europe's largest independent truck tyre retreader. Est. 1950. 12-acre site in Grantham. Owned by Zenises Group. Certified B Corp.</t>
+          <t>Europe's largest independent tyre retreader. Specialises in truck and commercial vehicle tyre retreading. Based in Grantham. Owned by Zenises Group.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vaculug.com</t>
+          <t>www.vaculug.com</t>
         </is>
       </c>
     </row>
@@ -701,12 +697,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Multinational tyre company (Dubai/London). Distributes Westlake, Triangle, iLink truck tyre brands. Owns Vaculug retreading.</t>
+          <t>Tyre manufacturer and distributor group. Owns Vaculug (Europe's largest independent retreader). Active in commercial/truck tyre market.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>zenises.com</t>
+          <t>www.zenises.com</t>
         </is>
       </c>
     </row>
@@ -718,7 +714,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>INDEPENDENT TYRE DISTRIBUTORS NETWORK LIMITED</t>
+          <t>INDEPENDENT TYRE DISTRIBUTORS NETWORK LTD</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -743,29 +739,29 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>UK's largest independent 24-hour truck tyre breakdown network. 600+ member dealers. 122,000+ breakdowns in 2023. Member-owned since 1985.</t>
+          <t>Network of 600+ independent tyre dealers providing nationwide 24-hour breakdown coverage for commercial vehicles/trucks. Key industry infrastructure for truck tyre services.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>itdn.org.uk</t>
+          <t>www.itdn.co.uk</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>02799338</t>
+          <t>02531072</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PACCAR PARTS U.K. LIMITED</t>
+          <t>G &amp; S TYRE SERVICES LIMITED</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TRP (Truck, Trailer &amp; Bus Parts)</t>
+          <t>GS Tyres</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -775,7 +771,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -785,29 +781,29 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>TRP brand sells truck tyres + 157,000 parts for all truck/trailer/bus makes via DAF dealer network. PACCAR subsidiary.</t>
+          <t>Commercial truck tyre specialist in Barking, East London. Fleet of 16 mobile fitting vans + 2 artic trucks. Operates Marangoni RINGTREAD retreading factory (Reg 109 approved). First independent commercial retreading specialist to join NTDA. Founded 1990.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>trp.eu</t>
+          <t>www.gstyres.co.uk</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07013332</t>
+          <t>SC156534</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>KAL TIRE (UK) LIMITED</t>
+          <t>R &amp; J STRANG TYRE SERVICES LIMITED</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kal Tire (second entity)</t>
+          <t>R&amp;J Strang</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -827,29 +823,29 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Second UK entity for Kal Tire OTR tyre operations. Same Derbyshire address.</t>
+          <t>Commercial fleet tyre management specialist across Scotland and England. Wholly owned subsidiary of Continental Tyre Group since 2019. 8 depots (Hamilton, Irvine, Broxburn, Leeds, Lutterworth, Luton, Nottingham, Washington). Part of Conti360 network.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>kaltiremining.com</t>
+          <t>www.rjstrang.co.uk</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>05648203</t>
+          <t>06839153</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FIT4FLEET LIMITED</t>
+          <t>FULLER TYRES LIMITED</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fit4Fleet</t>
+          <t>Fuller Tyres</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -859,7 +855,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -869,29 +865,29 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>One of UK's largest tyre management companies. 1,100+ centres, 2,000+ mobile fitting vans. Est. 2001. Independent.</t>
+          <t>Commercial vehicle tyre service provider in Surrey. Tyre fitting and maintenance for commercial vehicles including trucks.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>fit4fleet.co.uk</t>
+          <t>fullertyres.co.uk</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>00442022</t>
+          <t>00985614</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>R. H. CLAYDON LIMITED</t>
+          <t>TANVIC GROUP LIMITED</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>R.H. Claydon</t>
+          <t>Tanvic</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -911,39 +907,39 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Specialist tyre wholesaler since 1953. Exclusive UK distributor for Yokohama truck/bus tyres (2024). 8 warehouse locations.</t>
+          <t>One of UK's largest independent automotive aftermarket suppliers. 20+ branches across Midlands/East Anglia/South Yorkshire. 260+ staff, 140+ vehicles. Truck/commercial tyre fitting, fleet management, 24/7/365 breakdown. ITDN member. Stock 150,000+ tyres.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>rhc.co.uk</t>
+          <t>www.tanvic.co.uk</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SC479879</t>
+          <t>00944192</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SOLTYRE LIMITED</t>
+          <t>R.H.CLAYDON LIMITED</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Soltyre</t>
+          <t>R.H. Claydon</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Maybe</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -953,29 +949,29 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>One of UK's largest independent tyre suppliers. Truck/lorry tyres, fleet management, 24-hour commercial call-out. Founded 2009, Scotland.</t>
+          <t>One of UK's premier tyre wholesalers (wholesale trade of tyres and motor vehicle parts). Founded 1953. Primarily a wholesaler rather than truck tyre retail specialist - needs verification of truck tyre focus vs general wholesale.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>soltyre.co.uk</t>
+          <t>www.rhc.co.uk</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>12141498</t>
+          <t>OC309957</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PROMETEON TYRE GROUP UK LIMITED</t>
+          <t>PB TYRES UK LLP</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Prometeon (ex-Pirelli Industrial)</t>
+          <t>PB Tyres</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -995,29 +991,29 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pirelli industrial division spin-off. SuperTruck dealer network launched UK 2023. Sells Pirelli truck tyres under licence.</t>
+          <t>One of UK's biggest truck tyre casing specialists. Family-run commercial tyre wholesaler with 40+ years experience. Manufacture own 'Emerald re-treads' brand. Truck tyre sales, repair, remoulding, casing sales. Own delivery fleet across UK and internationally.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>prometeon.com</t>
+          <t>www.pbtyres.uk</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>02253505</t>
+          <t>03873873</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ALTEREVER LIMITED</t>
+          <t>T I A (GB) LIMITED</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Alterever</t>
+          <t>TIA Group / TIA Tyres</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1027,7 +1023,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1037,25 +1033,29 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Independent retreading company. Founded 1974, East Yorkshire. BTMA retread member. Truck tyre retreading specialist.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Wholesale tyre and wheel supplier. TIA Group offers tyres for cars, trucks, buses, and vans. Parent company owning TIA Tyres Ltd, TIA UK Tyres Ltd, TIA Agri Ltd, and others.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>www.thetiagroup.com</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>02618192</t>
+          <t>05973368</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FULLER TYRE SERVICE LIMITED</t>
+          <t>FIT4FLEET LIMITED</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Fuller Tyres</t>
+          <t>Fit4fleet</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1075,29 +1075,29 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Multi-brand tyre management specialists. Supply and fit new/retread truck tyres for commercial fleets. 1,000+ tyres per warehouse.</t>
+          <t>Mobile tyre fitting and fleet tyre management. 24/7/365 tyre replacement service. Full tyre management for fleets of all sizes (car, van, truck). Network of 100+ fitting centres and 400 mobile vans.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>fullertyres.co.uk</t>
+          <t>www.fit4fleet.co.uk</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08279445</t>
+          <t>05011012</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TD TYRES LIMITED</t>
+          <t>TYRENET (UK) LIMITED</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>TD Tyres</t>
+          <t>Tyrenet</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1117,29 +1117,29 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Truck, coach, bus tyre supplier (premium/mid/budget). 14+ years. 24/7 UK and European breakdown service. 1hr target response.</t>
+          <t>Fleet tyre management and 24-hour mobile truck tyre fitting. Network of 1,000+ depots and 500+ dealers. 90-minute mobile commercial tyre fitting response for all HGV sizes. Cloud-based Tyre Management Portal. UK/European breakdown via TEN network (3,400+ locations, 14 countries).</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>tdtyres.com</t>
+          <t>tyrenet.net</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>00290799</t>
+          <t>09792282</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TANVIC TYRE AND AUTOCENTRE LIMITED</t>
+          <t>PROMETEON TYRE GROUP UK LIMITED</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tanvic</t>
+          <t>Prometeon</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1159,344 +1159,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>East Midlands commercial truck tyre supplier. ITDN member. National breakdown coverage through network.</t>
+          <t>UK arm of Prometeon Tyre Group (spun off from Pirelli industrial division 2017). Only tyre manufacturer focused entirely on commercial/transport, agricultural, and OTR sectors. Sells under PIRELLI and FORMULA brands (licence) plus own brands. NTDA Tyre Manufacturer of the Year 2025.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>tanvic.co.uk</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>03522684</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>COUNTY TYRE HOLDINGS LIMITED</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>County Tyres / The Tyre Group</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Industry research - not in Companies House keyword search</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Part of The Tyre Group (UK's largest independent tyre retailer, 116+ locations). Includes commercial tyre operations.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>05151968</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>TYRENET LIMITED</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Tyrenet</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Industry research - not in Companies House keyword search</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>24-hour mobile truck tyre fitting network. 1,000+ dealers. 90-min response. Exclusive service partner for Hankook Truck Masters.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>tyrenet.net</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>01490917</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>WILTSHIRE TYRES LIMITED</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Wiltshire Tyres</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Industry research - not in Companies House keyword search</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Leading South-West independent commercial tyre supplier. Local and national breakdown coverage via network partnerships.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>wiltshiretyres.co.uk</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>04119893</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>POTTERIES TYRES LIMITED</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Potteries Tyres</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Industry research - not in Companies House keyword search</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Fleet tyre management for truck/trailer fleets. Stoke-on-Trent area. 24/7/365 service. Uses 'Tyre Ops' management software.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>potteriestyres.co.uk</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>02899866</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>GROUPTYRE (UK) LIMITED</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Grouptyre</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Industry research - not in Companies House keyword search</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>UK's leading independent tyre wholesaler. Regional partners: Bush Tyres, Car Tyrestore, Kenway Tyres, EG Wholesale, ETB Wholesale.</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>grouptyre.co.uk</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>06428539</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>BIG TYRES LIMITED</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Big Tyres</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Industry research - not in Companies House keyword search</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Online truck/bus tyre retailer with mobile fitting network covering mainland GB.</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>bigtyres.co.uk</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>SC191780</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>R &amp; J STRANG TYRE SERVICES LIMITED</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>R&amp;J Strang</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Industry research - not in Companies House keyword search</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Scottish truck tyre specialist. Continental-owned. Supplies Continental, Bandvulc, Uniroyal truck tyres.</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>rjstrang.co.uk</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>01099960</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>SOUTH EASTERN TYRES (HOLDINGS) LIMITED</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Setyres Commercial</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Industry research - not in Companies House keyword search</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Truck and bus tyre supply and fitting. Sussex/Kent/Surrey. Fleet services including recutting, inspections, roadside breakdown.</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>setyrescommercial.com</t>
+          <t>www.prometeon.com/UK/en_UK</t>
         </is>
       </c>
     </row>

--- a/backend/truck_tyre_specialists_additional.xlsx
+++ b/backend/truck_tyre_specialists_additional.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Additional Specialists" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,7 +578,6 @@
           <t>UK's leading truck tyre wholesaler. Major supplier of commercial vehicle tyres to the UK trade.</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1165,6 +1164,48 @@
       <c r="H18" t="inlineStr">
         <is>
           <t>www.prometeon.com/UK/en_UK</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>04012599</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>MURFITTS INDUSTRIES LIMITED</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Murfitts Industries</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Maybe</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Industry research - UK's largest tyre collector/processor</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>UK's largest tyre recycler. 20M tyres/year, 100,000 tonnes. Owned by ETEL (Kwik Fit/Itochu group). Part of commercial tyre ecosystem but primarily recycling, not fitting.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>murfittsindustries.com</t>
         </is>
       </c>
     </row>
